--- a/data/trans_dic/P43C-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P43C-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que alguna vez le han realizado una citología vaginal</t>
+          <t>Población a la que alguna vez le han realizado una citología vaginal (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>73,62%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>81,64%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>78,96%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>74,95%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>68,08; 78,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>76,78; 85,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74,37; 83,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>69,8; 78,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,38; 78,03</t>
+          <t>68,08; 78,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,59; 85,86</t>
+          <t>76,78; 85,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,08; 82,94</t>
+          <t>74,37; 83,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>70,09; 79,29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68,38; 78,03</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>76,59; 85,86</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74,08; 82,94</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>70,09; 79,29</t>
+          <t>69,8; 78,99</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75,58%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>67,73%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>81,76%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>81,45%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>75,58%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,37; 72,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,18; 85,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>76,95; 85,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,17; 79,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,66; 72,04</t>
+          <t>62,37; 72,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,23; 85,8</t>
+          <t>77,18; 85,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,13; 85,51</t>
+          <t>76,95; 85,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,11; 80,07</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>62,66; 72,04</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>77,23; 85,8</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>77,13; 85,51</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>71,11; 80,07</t>
+          <t>71,17; 79,9</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>62,14%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>65,16%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>68,34%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>72,12%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>62,14%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>57,22; 72,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,19; 73,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64,08; 79,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>54,36; 69,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,75; 71,36</t>
+          <t>57,22; 72,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,23; 73,86</t>
+          <t>62,19; 73,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,58; 79,19</t>
+          <t>64,08; 79,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,19; 68,93</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>57,75; 71,36</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>62,23; 73,86</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>63,58; 79,19</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>54,19; 68,93</t>
+          <t>54,36; 69,87</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47,24%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>72,47%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>70,12%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>47,24%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,94; 60,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>68,83; 75,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,92; 73,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,87; 65,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,77; 59,93</t>
+          <t>52,94; 60,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,63; 75,34</t>
+          <t>68,83; 75,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,83; 73,49</t>
+          <t>66,92; 73,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,72; 65,92</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>52,77; 59,93</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>68,63; 75,34</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>66,83; 73,49</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>20,72; 65,92</t>
+          <t>19,87; 65,94</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>59,9%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>55,76%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>61,97%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>59,9%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,12; 59,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60,26; 67,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>57,92; 65,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,57; 70,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,4; 59,78</t>
+          <t>51,12; 59,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,49; 67,57</t>
+          <t>60,26; 67,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,18; 65,33</t>
+          <t>57,92; 65,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>52,79; 71,65</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51,4; 59,78</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>60,49; 67,57</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>58,18; 65,33</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>52,79; 71,65</t>
+          <t>52,57; 70,86</t>
         </is>
       </c>
     </row>
@@ -1349,22 +1113,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,26 +1147,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>42,97%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>40,64%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>50,28%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>48,28%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>42,97%</t>
         </is>
@@ -1417,62 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,99; 43,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,12; 53,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,1; 51,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,4; 46,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,8; 43,45</t>
+          <t>37,99; 43,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,13; 53,33</t>
+          <t>47,12; 53,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,16; 51,32</t>
+          <t>45,1; 51,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,34; 46,73</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>37,8; 43,45</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>47,13; 53,33</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>45,16; 51,32</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>39,34; 46,73</t>
+          <t>39,4; 46,84</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1213,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,26 +1247,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>55,99%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>53,8%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>65,11%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>63,93%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>55,99%</t>
         </is>
@@ -1557,62 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52,17; 55,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,32; 66,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,21; 65,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,26; 61,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,96; 55,43</t>
+          <t>52,17; 55,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,36; 66,67</t>
+          <t>63,32; 66,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,2; 65,6</t>
+          <t>62,21; 65,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,7; 61,69</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>51,96; 55,43</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>63,36; 66,67</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>62,2; 65,6</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>44,7; 61,69</t>
+          <t>44,26; 61,44</t>
         </is>
       </c>
     </row>
@@ -1624,17 +1308,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1647,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1660,22 +1343,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que alguna vez le han realizado una citología vaginal</t>
+          <t>Población a la que alguna vez le han realizado una citología vaginal (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,20 +1362,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1737,26 +1408,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1773,10 +1424,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1791,22 +1438,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>370</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1825,26 +1472,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>370</t>
         </is>
@@ -1859,22 +1486,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222314</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>255926</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>230933</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1893,26 +1520,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>230933</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>222314</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>255926</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>271170</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>230933</t>
         </is>
@@ -1927,62 +1534,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>205579; 236754</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>240681; 268988</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>255426; 285371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>215083; 243378</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>206497; 235625</t>
+          <t>205579; 236754</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>240085; 269163</t>
+          <t>240681; 268988</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>254423; 284825</t>
+          <t>255426; 285371</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>215956; 244322</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>206497; 235625</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>240085; 269163</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>254423; 284825</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>215956; 244322</t>
+          <t>215083; 243378</t>
         </is>
       </c>
     </row>
@@ -1999,22 +1586,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>286</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>321</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2033,26 +1620,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>321</t>
         </is>
@@ -2067,22 +1634,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248606</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271931</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301605</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2101,26 +1668,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>207621</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>248606</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>271931</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>301605</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>207621</t>
         </is>
@@ -2135,62 +1682,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>228930; 265036</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>256716; 285182</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>284941; 316335</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>195523; 219510</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>230000; 264427</t>
+          <t>228930; 265036</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>256874; 285373</t>
+          <t>256716; 285182</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>285624; 316623</t>
+          <t>284941; 316335</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>195356; 219976</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>230000; 264427</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>256874; 285373</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>285624; 316623</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>195356; 219976</t>
+          <t>195523; 219510</t>
         </is>
       </c>
     </row>
@@ -2207,22 +1734,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>167</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2241,26 +1768,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>130</t>
         </is>
@@ -2275,22 +1782,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109319</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>175641</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2309,26 +1816,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>73507</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>109319</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>175641</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>119804</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>73507</t>
         </is>
@@ -2343,62 +1830,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>95997; 120923</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>159825; 189309</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>106457; 131554</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64296; 82654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>96894; 119727</t>
+          <t>95997; 120923</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>159921; 189818</t>
+          <t>159825; 189309</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>105617; 131555</t>
+          <t>106457; 131554</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64096; 81538</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>96894; 119727</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>159921; 189818</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>105617; 131555</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>64096; 81538</t>
+          <t>64296; 82654</t>
         </is>
       </c>
     </row>
@@ -2415,22 +1882,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>391</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>509</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>556</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2449,26 +1916,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>574</t>
         </is>
@@ -2483,22 +1930,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>400973</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>551897</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>574470</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>358128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2517,26 +1964,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>358128</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>400973</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>551897</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>574470</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>358128</t>
         </is>
@@ -2551,62 +1978,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>375226; 429768</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>524173; 574476</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>548207; 599865</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>150613; 499868</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>374037; 424802</t>
+          <t>375226; 429768</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>522626; 573790</t>
+          <t>524173; 574476</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>547482; 602055</t>
+          <t>548207; 599865</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>157041; 499744</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>374037; 424802</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>522626; 573790</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>547482; 602055</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>157041; 499744</t>
+          <t>150613; 499868</t>
         </is>
       </c>
     </row>
@@ -2623,22 +2030,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>299</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>443</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>432</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2657,26 +2064,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>520</t>
         </is>
@@ -2691,22 +2078,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311915</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>482176</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>452968</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2725,26 +2112,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>403893</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>311915</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>482176</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>452968</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>403893</t>
         </is>
@@ -2759,62 +2126,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>285961; 335628</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>454535; 507809</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>423387; 477134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>354440; 477798</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>287570; 334446</t>
+          <t>285961; 335628</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>456297; 509666</t>
+          <t>454535; 507809</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>425252; 477534</t>
+          <t>423387; 477134</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>355946; 483100</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>287570; 334446</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>456297; 509666</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>425252; 477534</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>355946; 483100</t>
+          <t>354440; 477798</t>
         </is>
       </c>
     </row>
@@ -2831,22 +2178,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>487</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>514</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2865,26 +2212,6 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>452</t>
         </is>
@@ -2899,22 +2226,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>496149</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>551209</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>513553</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>262551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2933,26 +2260,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>262551</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>496149</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>551209</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>513553</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>262551</t>
         </is>
@@ -2967,62 +2274,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>463813; 533547</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>516563; 582654</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>479745; 550832</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>240761; 286239</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>461470; 530471</t>
+          <t>463813; 533547</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>516583; 584606</t>
+          <t>516563; 582654</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>480401; 545914</t>
+          <t>479745; 550832</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>240365; 285517</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>461470; 530471</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>516583; 584606</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>480401; 545914</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>240365; 285517</t>
+          <t>240761; 286239</t>
         </is>
       </c>
     </row>
@@ -3039,22 +2326,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3073,26 +2360,6 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2367</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2103</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2115</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2367</t>
         </is>
@@ -3107,22 +2374,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1789276</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2288781</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2233570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1536633</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3141,26 +2408,6 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1536633</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1789276</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>2288781</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2233570</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>1536633</t>
         </is>
@@ -3175,62 +2422,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1735153; 1849331</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2225757; 2341574</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2173571; 2292662</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1214836; 1686282</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1728245; 1843654</t>
+          <t>1735153; 1849331</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2227223; 2343672</t>
+          <t>2225757; 2341574</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2173249; 2291841</t>
+          <t>2173571; 2292662</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1226833; 1693223</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1728245; 1843654</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2227223; 2343672</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>2173249; 2291841</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>1226833; 1693223</t>
+          <t>1214836; 1686282</t>
         </is>
       </c>
     </row>
@@ -3242,16 +2469,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/P43C-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P43C-Clase-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,08; 78,4</t>
+          <t>68,51; 78,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,78; 85,81</t>
+          <t>76,07; 85,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,37; 83,09</t>
+          <t>74,26; 83,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69,8; 78,99</t>
+          <t>69,7; 78,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,08; 78,4</t>
+          <t>68,51; 78,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,78; 85,81</t>
+          <t>76,07; 85,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,37; 83,09</t>
+          <t>74,26; 83,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,8; 78,99</t>
+          <t>69,7; 78,72</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,81%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,37; 72,21</t>
+          <t>62,38; 72,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,18; 85,74</t>
+          <t>77,15; 85,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,95; 85,43</t>
+          <t>77,1; 85,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71,17; 79,9</t>
+          <t>70,62; 79,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,37; 72,21</t>
+          <t>62,38; 72,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,18; 85,74</t>
+          <t>77,15; 85,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,95; 85,43</t>
+          <t>77,1; 85,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,17; 79,9</t>
+          <t>70,62; 79,0</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,86%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,22; 72,07</t>
+          <t>57,72; 71,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,19; 73,66</t>
+          <t>62,06; 74,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,08; 79,19</t>
+          <t>64,22; 79,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54,36; 69,87</t>
+          <t>54,33; 69,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,22; 72,07</t>
+          <t>57,72; 71,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,19; 73,66</t>
+          <t>62,06; 74,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,08; 79,19</t>
+          <t>64,22; 79,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,36; 69,87</t>
+          <t>54,33; 69,17</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,94; 60,64</t>
+          <t>52,85; 60,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68,83; 75,43</t>
+          <t>69,1; 75,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66,92; 73,22</t>
+          <t>66,42; 73,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,87; 65,94</t>
+          <t>61,13; 67,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,94; 60,64</t>
+          <t>52,85; 60,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,83; 75,43</t>
+          <t>69,1; 75,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,92; 73,22</t>
+          <t>66,42; 73,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,87; 65,94</t>
+          <t>61,13; 67,77</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>51,04%</t>
         </is>
       </c>
     </row>
@@ -1061,49 +1061,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>51,12; 59,99</t>
+          <t>51,28; 59,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,26; 67,32</t>
+          <t>60,23; 67,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,92; 65,27</t>
+          <t>58,13; 65,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52,57; 70,86</t>
+          <t>47,67; 54,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,12; 59,99</t>
+          <t>51,28; 59,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,26; 67,32</t>
+          <t>60,23; 67,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,92; 65,27</t>
+          <t>58,13; 65,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>52,57; 70,86</t>
+          <t>47,67; 54,19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,08%</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,99; 43,7</t>
+          <t>38,02; 43,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,12; 53,15</t>
+          <t>47,05; 53,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,1; 51,79</t>
+          <t>45,09; 51,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39,4; 46,84</t>
+          <t>38,61; 46,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,99; 43,7</t>
+          <t>38,02; 43,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,12; 53,15</t>
+          <t>47,05; 53,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,1; 51,79</t>
+          <t>45,09; 51,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,4; 46,84</t>
+          <t>38,61; 46,0</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>57,97%</t>
         </is>
       </c>
     </row>
@@ -1261,42 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>52,17; 55,6</t>
+          <t>52,2; 55,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63,32; 66,61</t>
+          <t>63,55; 66,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62,21; 65,62</t>
+          <t>62,4; 65,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44,26; 61,44</t>
+          <t>55,94; 59,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,17; 55,6</t>
+          <t>52,2; 55,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,32; 66,61</t>
+          <t>63,55; 66,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,21; 65,62</t>
+          <t>62,4; 65,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,26; 61,44</t>
+          <t>55,94; 59,59</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230933</t>
+          <t>250586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>230933</t>
+          <t>250586</t>
         </is>
       </c>
     </row>
@@ -1534,42 +1534,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>205579; 236754</t>
+          <t>206896; 236523</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>240681; 268988</t>
+          <t>238472; 268894</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>255426; 285371</t>
+          <t>255030; 285490</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>215083; 243378</t>
+          <t>235249; 265693</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>205579; 236754</t>
+          <t>206896; 236523</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>240681; 268988</t>
+          <t>238472; 268894</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>255426; 285371</t>
+          <t>255030; 285490</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>215083; 243378</t>
+          <t>235249; 265693</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>230110</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>230110</t>
         </is>
       </c>
     </row>
@@ -1682,42 +1682,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>228930; 265036</t>
+          <t>228977; 266345</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>256716; 285182</t>
+          <t>256616; 285670</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>284941; 316335</t>
+          <t>285487; 315927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>195523; 219510</t>
+          <t>217237; 243004</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>228930; 265036</t>
+          <t>228977; 266345</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>256716; 285182</t>
+          <t>256616; 285670</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>284941; 316335</t>
+          <t>285487; 315927</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>195523; 219510</t>
+          <t>217237; 243004</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>81404</t>
         </is>
       </c>
     </row>
@@ -1830,42 +1830,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>95997; 120923</t>
+          <t>96850; 120282</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>159825; 189309</t>
+          <t>159499; 190832</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106457; 131554</t>
+          <t>106680; 132698</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64296; 82654</t>
+          <t>71499; 91029</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>95997; 120923</t>
+          <t>96850; 120282</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>159825; 189309</t>
+          <t>159499; 190832</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>106457; 131554</t>
+          <t>106680; 132698</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64296; 82654</t>
+          <t>71499; 91029</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358128</t>
+          <t>397476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>358128</t>
+          <t>397476</t>
         </is>
       </c>
     </row>
@@ -1978,42 +1978,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>375226; 429768</t>
+          <t>374578; 426954</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>524173; 574476</t>
+          <t>526274; 577057</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>548207; 599865</t>
+          <t>544157; 600560</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>150613; 499868</t>
+          <t>376978; 417977</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>375226; 429768</t>
+          <t>374578; 426954</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>524173; 574476</t>
+          <t>526274; 577057</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>548207; 599865</t>
+          <t>544157; 600560</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>150613; 499868</t>
+          <t>376978; 417977</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>403893</t>
+          <t>326666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>403893</t>
+          <t>326666</t>
         </is>
       </c>
     </row>
@@ -2126,49 +2126,49 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>285961; 335628</t>
+          <t>286868; 335353</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>454535; 507809</t>
+          <t>454346; 507711</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>423387; 477134</t>
+          <t>424892; 480678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>354440; 477798</t>
+          <t>305091; 346868</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>285961; 335628</t>
+          <t>286868; 335353</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>454535; 507809</t>
+          <t>454346; 507711</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>423387; 477134</t>
+          <t>424892; 480678</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>354440; 477798</t>
+          <t>305091; 346868</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262551</t>
+          <t>284273</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>262551</t>
+          <t>284273</t>
         </is>
       </c>
     </row>
@@ -2274,42 +2274,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>463813; 533547</t>
+          <t>464187; 530331</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>516563; 582654</t>
+          <t>515782; 584153</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>479745; 550832</t>
+          <t>479633; 545760</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240761; 286239</t>
+          <t>260813; 310697</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>463813; 533547</t>
+          <t>464187; 530331</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>516563; 582654</t>
+          <t>515782; 584153</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>479745; 550832</t>
+          <t>479633; 545760</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>240761; 286239</t>
+          <t>260813; 310697</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1536633</t>
+          <t>1570516</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1536633</t>
+          <t>1570516</t>
         </is>
       </c>
     </row>
@@ -2422,42 +2422,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1735153; 1849331</t>
+          <t>1736251; 1846946</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2225757; 2341574</t>
+          <t>2233972; 2348480</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2173571; 2292662</t>
+          <t>2180062; 2293272</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1214836; 1686282</t>
+          <t>1515550; 1614339</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1735153; 1849331</t>
+          <t>1736251; 1846946</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2225757; 2341574</t>
+          <t>2233972; 2348480</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2173571; 2292662</t>
+          <t>2180062; 2293272</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1214836; 1686282</t>
+          <t>1515550; 1614339</t>
         </is>
       </c>
     </row>
